--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
   <si>
     <t>날짜</t>
   </si>
@@ -61,40 +61,43 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-06</t>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>Riot Platforms, Inc.</t>
+  </si>
+  <si>
+    <t>MARA Holdings, Inc.</t>
+  </si>
+  <si>
+    <t>Coinbase Global, Inc.</t>
   </si>
   <si>
     <t>Bitcoin USD</t>
   </si>
   <si>
-    <t>Riot Platforms, Inc.</t>
-  </si>
-  <si>
-    <t>MARA Holdings, Inc.</t>
-  </si>
-  <si>
-    <t>Coinbase Global, Inc.</t>
-  </si>
-  <si>
     <t>Strategy Inc</t>
   </si>
   <si>
+    <t>RIOT</t>
+  </si>
+  <si>
+    <t>MARA</t>
+  </si>
+  <si>
+    <t>COIN</t>
+  </si>
+  <si>
     <t>BTC-USD</t>
   </si>
   <si>
-    <t>RIOT</t>
-  </si>
-  <si>
-    <t>MARA</t>
-  </si>
-  <si>
-    <t>COIN</t>
-  </si>
-  <si>
     <t>MSTR</t>
   </si>
   <si>
     <t>Pattern</t>
+  </si>
+  <si>
+    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -519,28 +522,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>89623.46000000001</v>
+        <v>15.46</v>
       </c>
       <c r="E2">
-        <v>59.9</v>
+        <v>60.6</v>
       </c>
       <c r="F2">
-        <v>3.83</v>
+        <v>1.58</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="I2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J2">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="K2">
-        <v>57.7</v>
+        <v>60.4</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,10 +552,10 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -566,16 +569,16 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>14.94</v>
+        <v>12.32</v>
       </c>
       <c r="E3">
-        <v>57.3</v>
+        <v>53.5</v>
       </c>
       <c r="F3">
-        <v>-7.38</v>
+        <v>3.44</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H3">
         <v>50</v>
@@ -584,22 +587,22 @@
         <v>60</v>
       </c>
       <c r="J3">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="K3">
-        <v>54.7</v>
+        <v>56.4</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
       </c>
       <c r="M3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N3">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -613,40 +616,40 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>11.74</v>
+        <v>279.76</v>
       </c>
       <c r="E4">
-        <v>48.1</v>
+        <v>58.2</v>
       </c>
       <c r="F4">
-        <v>-0.59</v>
+        <v>6.27</v>
       </c>
       <c r="G4">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H4">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="I4">
+        <v>60</v>
+      </c>
+      <c r="J4">
         <v>63</v>
       </c>
-      <c r="J4">
-        <v>70</v>
-      </c>
       <c r="K4">
-        <v>49.9</v>
+        <v>56.4</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
       </c>
       <c r="M4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N4">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -660,40 +663,40 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>269.73</v>
+        <v>93674.42</v>
       </c>
       <c r="E5">
-        <v>44.1</v>
+        <v>62.8</v>
       </c>
       <c r="F5">
-        <v>-1.13</v>
+        <v>1.66</v>
       </c>
       <c r="G5">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H5">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="I5">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J5">
         <v>50</v>
       </c>
       <c r="K5">
-        <v>48.7</v>
+        <v>52.4</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
       </c>
       <c r="M5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N5">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -707,40 +710,40 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>178.99</v>
+        <v>193.57</v>
       </c>
       <c r="E6">
-        <v>40.1</v>
+        <v>43.6</v>
       </c>
       <c r="F6">
-        <v>1.02</v>
+        <v>6.75</v>
       </c>
       <c r="G6">
+        <v>50</v>
+      </c>
+      <c r="H6">
+        <v>50</v>
+      </c>
+      <c r="I6">
+        <v>43</v>
+      </c>
+      <c r="J6">
         <v>40</v>
       </c>
-      <c r="H6">
-        <v>36</v>
-      </c>
-      <c r="I6">
-        <v>40</v>
-      </c>
-      <c r="J6">
-        <v>36</v>
-      </c>
       <c r="K6">
-        <v>43.7</v>
+        <v>46.6</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
       </c>
       <c r="M6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N6">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
   <si>
     <t>날짜</t>
   </si>
@@ -67,37 +67,34 @@
     <t>Riot Platforms, Inc.</t>
   </si>
   <si>
+    <t>Coinbase Global, Inc.</t>
+  </si>
+  <si>
+    <t>Bitcoin USD</t>
+  </si>
+  <si>
     <t>MARA Holdings, Inc.</t>
   </si>
   <si>
-    <t>Coinbase Global, Inc.</t>
-  </si>
-  <si>
-    <t>Bitcoin USD</t>
-  </si>
-  <si>
     <t>Strategy Inc</t>
   </si>
   <si>
     <t>RIOT</t>
   </si>
   <si>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>BTC-USD</t>
+  </si>
+  <si>
     <t>MARA</t>
   </si>
   <si>
-    <t>COIN</t>
-  </si>
-  <si>
-    <t>BTC-USD</t>
-  </si>
-  <si>
     <t>MSTR</t>
   </si>
   <si>
     <t>Pattern</t>
-  </si>
-  <si>
-    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -522,13 +519,13 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>15.46</v>
+        <v>15.51</v>
       </c>
       <c r="E2">
-        <v>60.6</v>
+        <v>60.8</v>
       </c>
       <c r="F2">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="G2">
         <v>60</v>
@@ -543,7 +540,7 @@
         <v>73</v>
       </c>
       <c r="K2">
-        <v>60.4</v>
+        <v>59.9</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -552,10 +549,10 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -569,19 +566,19 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>12.32</v>
+        <v>277.36</v>
       </c>
       <c r="E3">
-        <v>53.5</v>
+        <v>57.3</v>
       </c>
       <c r="F3">
-        <v>3.44</v>
+        <v>5.36</v>
       </c>
       <c r="G3">
         <v>60</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I3">
         <v>60</v>
@@ -590,19 +587,19 @@
         <v>63</v>
       </c>
       <c r="K3">
-        <v>56.4</v>
+        <v>55.9</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
       </c>
       <c r="M3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3">
+        <v>46.17217538625081</v>
+      </c>
+      <c r="O3" t="s">
         <v>28</v>
-      </c>
-      <c r="N3">
-        <v>48.11568981226033</v>
-      </c>
-      <c r="O3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -616,40 +613,40 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>279.76</v>
+        <v>92523.87</v>
       </c>
       <c r="E4">
-        <v>58.2</v>
+        <v>61</v>
       </c>
       <c r="F4">
-        <v>6.27</v>
+        <v>0.41</v>
       </c>
       <c r="G4">
         <v>60</v>
       </c>
       <c r="H4">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="I4">
+        <v>56</v>
+      </c>
+      <c r="J4">
         <v>60</v>
       </c>
-      <c r="J4">
-        <v>63</v>
-      </c>
       <c r="K4">
-        <v>56.4</v>
+        <v>54.3</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
       </c>
       <c r="M4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4">
+        <v>46.17217538625081</v>
+      </c>
+      <c r="O4" t="s">
         <v>28</v>
-      </c>
-      <c r="N4">
-        <v>48.11568981226033</v>
-      </c>
-      <c r="O4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -663,40 +660,40 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>93674.42</v>
+        <v>12.25</v>
       </c>
       <c r="E5">
-        <v>62.8</v>
+        <v>53</v>
       </c>
       <c r="F5">
-        <v>1.66</v>
+        <v>2.85</v>
       </c>
       <c r="G5">
         <v>60</v>
       </c>
       <c r="H5">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I5">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J5">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K5">
-        <v>52.4</v>
+        <v>54.3</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
       </c>
       <c r="M5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5">
+        <v>46.17217538625081</v>
+      </c>
+      <c r="O5" t="s">
         <v>28</v>
-      </c>
-      <c r="N5">
-        <v>48.11568981226033</v>
-      </c>
-      <c r="O5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -710,40 +707,40 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>193.57</v>
+        <v>188.99</v>
       </c>
       <c r="E6">
-        <v>43.6</v>
+        <v>41</v>
       </c>
       <c r="F6">
-        <v>6.75</v>
+        <v>4.22</v>
       </c>
       <c r="G6">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H6">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="I6">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J6">
         <v>40</v>
       </c>
       <c r="K6">
-        <v>46.6</v>
+        <v>41.9</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
       </c>
       <c r="M6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6">
+        <v>46.17217538625081</v>
+      </c>
+      <c r="O6" t="s">
         <v>28</v>
-      </c>
-      <c r="N6">
-        <v>48.11568981226033</v>
-      </c>
-      <c r="O6" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-10</t>
+    <t>2025-12-15</t>
   </si>
   <si>
     <t>Riot Platforms, Inc.</t>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>15.51</v>
+        <v>15.3</v>
       </c>
       <c r="E2">
-        <v>60.8</v>
+        <v>69.3</v>
       </c>
       <c r="F2">
-        <v>1.91</v>
+        <v>2.41</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I2">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="J2">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="K2">
-        <v>59.9</v>
+        <v>57.4</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>277.36</v>
+        <v>267.46</v>
       </c>
       <c r="E3">
-        <v>57.3</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F3">
-        <v>5.36</v>
+        <v>-0.84</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="I3">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J3">
         <v>63</v>
       </c>
       <c r="K3">
-        <v>55.9</v>
+        <v>54.4</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>92523.87</v>
+        <v>89047.32000000001</v>
       </c>
       <c r="E4">
-        <v>61</v>
+        <v>47.2</v>
       </c>
       <c r="F4">
-        <v>0.41</v>
+        <v>-3.93</v>
       </c>
       <c r="G4">
+        <v>40</v>
+      </c>
+      <c r="H4">
+        <v>50</v>
+      </c>
+      <c r="I4">
         <v>60</v>
-      </c>
-      <c r="H4">
-        <v>56</v>
-      </c>
-      <c r="I4">
-        <v>56</v>
       </c>
       <c r="J4">
         <v>60</v>
       </c>
       <c r="K4">
-        <v>54.3</v>
+        <v>50.2</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>12.25</v>
+        <v>11.52</v>
       </c>
       <c r="E5">
-        <v>53</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F5">
-        <v>2.85</v>
+        <v>-1.87</v>
       </c>
       <c r="G5">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H5">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="I5">
         <v>56</v>
       </c>
       <c r="J5">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="K5">
-        <v>54.3</v>
+        <v>48.6</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>188.99</v>
+        <v>176.45</v>
       </c>
       <c r="E6">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F6">
-        <v>4.22</v>
+        <v>-1.42</v>
       </c>
       <c r="G6">
         <v>40</v>
       </c>
       <c r="H6">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="I6">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J6">
         <v>40</v>
       </c>
       <c r="K6">
-        <v>41.9</v>
+        <v>40.6</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -61,37 +61,37 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-15</t>
+    <t>2025-12-29</t>
   </si>
   <si>
     <t>Riot Platforms, Inc.</t>
   </si>
   <si>
-    <t>Coinbase Global, Inc.</t>
+    <t>MARA Holdings, Inc.</t>
   </si>
   <si>
     <t>Bitcoin USD</t>
   </si>
   <si>
-    <t>MARA Holdings, Inc.</t>
-  </si>
-  <si>
     <t>Strategy Inc</t>
   </si>
   <si>
+    <t>Coinbase Global, Inc. - 3</t>
+  </si>
+  <si>
     <t>RIOT</t>
   </si>
   <si>
+    <t>MARA</t>
+  </si>
+  <si>
+    <t>BTC-USD</t>
+  </si>
+  <si>
+    <t>MSTR</t>
+  </si>
+  <si>
     <t>COIN</t>
-  </si>
-  <si>
-    <t>BTC-USD</t>
-  </si>
-  <si>
-    <t>MARA</t>
-  </si>
-  <si>
-    <t>MSTR</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>15.3</v>
+        <v>13.44</v>
       </c>
       <c r="E2">
-        <v>69.3</v>
+        <v>38.8</v>
       </c>
       <c r="F2">
-        <v>2.41</v>
+        <v>0.45</v>
       </c>
       <c r="G2">
+        <v>30</v>
+      </c>
+      <c r="H2">
+        <v>46</v>
+      </c>
+      <c r="I2">
         <v>60</v>
       </c>
-      <c r="H2">
+      <c r="J2">
         <v>63</v>
       </c>
-      <c r="I2">
-        <v>63</v>
-      </c>
-      <c r="J2">
-        <v>66</v>
-      </c>
       <c r="K2">
-        <v>57.4</v>
+        <v>48.6</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>267.46</v>
+        <v>9.59</v>
       </c>
       <c r="E3">
-        <v>64.90000000000001</v>
+        <v>25.1</v>
       </c>
       <c r="F3">
-        <v>-0.84</v>
+        <v>-1.03</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I3">
         <v>63</v>
       </c>
       <c r="J3">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K3">
-        <v>54.4</v>
+        <v>46.8</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>89047.32000000001</v>
+        <v>87259.53</v>
       </c>
       <c r="E4">
-        <v>47.2</v>
+        <v>54.2</v>
       </c>
       <c r="F4">
-        <v>-3.93</v>
+        <v>-0.4</v>
       </c>
       <c r="G4">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H4">
+        <v>56</v>
+      </c>
+      <c r="I4">
         <v>50</v>
       </c>
-      <c r="I4">
-        <v>60</v>
-      </c>
       <c r="J4">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="K4">
-        <v>50.2</v>
+        <v>44.6</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>11.52</v>
+        <v>158.81</v>
       </c>
       <c r="E5">
-        <v>64.09999999999999</v>
+        <v>34.7</v>
       </c>
       <c r="F5">
-        <v>-1.87</v>
+        <v>0.36</v>
       </c>
       <c r="G5">
+        <v>30</v>
+      </c>
+      <c r="H5">
+        <v>43</v>
+      </c>
+      <c r="I5">
+        <v>43</v>
+      </c>
+      <c r="J5">
         <v>40</v>
       </c>
-      <c r="H5">
-        <v>56</v>
-      </c>
-      <c r="I5">
-        <v>56</v>
-      </c>
-      <c r="J5">
-        <v>56</v>
-      </c>
       <c r="K5">
-        <v>48.6</v>
+        <v>41.8</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>176.45</v>
+        <v>236.9</v>
       </c>
       <c r="E6">
-        <v>54</v>
+        <v>26.5</v>
       </c>
       <c r="F6">
-        <v>-1.42</v>
+        <v>-0.96</v>
       </c>
       <c r="G6">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H6">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="I6">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J6">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="K6">
-        <v>40.6</v>
+        <v>39.8</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
   <si>
     <t>날짜</t>
   </si>
@@ -61,7 +61,10 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-29</t>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>Bitcoin USD</t>
   </si>
   <si>
     <t>Riot Platforms, Inc.</t>
@@ -70,13 +73,13 @@
     <t>MARA Holdings, Inc.</t>
   </si>
   <si>
-    <t>Bitcoin USD</t>
+    <t>Coinbase Global, Inc. - 3</t>
   </si>
   <si>
     <t>Strategy Inc</t>
   </si>
   <si>
-    <t>Coinbase Global, Inc. - 3</t>
+    <t>BTC-USD</t>
   </si>
   <si>
     <t>RIOT</t>
@@ -85,19 +88,19 @@
     <t>MARA</t>
   </si>
   <si>
-    <t>BTC-USD</t>
+    <t>COIN</t>
   </si>
   <si>
     <t>MSTR</t>
   </si>
   <si>
-    <t>COIN</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
+  </si>
+  <si>
+    <t>🤏 바닥권 접근 구간입니다.</t>
   </si>
   <si>
     <t>⚪ 중립 구간</t>
@@ -519,28 +522,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>13.44</v>
+        <v>91215.8</v>
       </c>
       <c r="E2">
-        <v>38.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F2">
-        <v>0.45</v>
+        <v>3.15</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I2">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J2">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="K2">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,10 +552,10 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -566,28 +569,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>9.59</v>
+        <v>14.16</v>
       </c>
       <c r="E3">
-        <v>25.1</v>
+        <v>40.2</v>
       </c>
       <c r="F3">
-        <v>-1.03</v>
+        <v>1.72</v>
       </c>
       <c r="G3">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H3">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I3">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="J3">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K3">
-        <v>46.8</v>
+        <v>44.5</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,10 +599,10 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -613,28 +616,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>87259.53</v>
+        <v>9.91</v>
       </c>
       <c r="E4">
-        <v>54.2</v>
+        <v>30.4</v>
       </c>
       <c r="F4">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="G4">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H4">
         <v>56</v>
       </c>
       <c r="I4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J4">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="K4">
-        <v>44.6</v>
+        <v>42.5</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,10 +646,10 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -660,40 +663,40 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>158.81</v>
+        <v>236.53</v>
       </c>
       <c r="E5">
-        <v>34.7</v>
+        <v>28.4</v>
       </c>
       <c r="F5">
-        <v>0.36</v>
+        <v>-1.33</v>
       </c>
       <c r="G5">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H5">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="I5">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="J5">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="K5">
-        <v>41.8</v>
+        <v>37.9</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
       </c>
       <c r="M5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N5">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -707,28 +710,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>236.9</v>
+        <v>157.16</v>
       </c>
       <c r="E6">
-        <v>26.5</v>
+        <v>29.2</v>
       </c>
       <c r="F6">
-        <v>-0.96</v>
+        <v>-0.98</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H6">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="I6">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="J6">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="K6">
-        <v>39.8</v>
+        <v>36.9</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,10 +740,10 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
   <si>
     <t>날짜</t>
   </si>
@@ -61,36 +61,36 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-05</t>
+    <t>2026-01-07</t>
+  </si>
+  <si>
+    <t>Riot Platforms, Inc.</t>
+  </si>
+  <si>
+    <t>Coinbase Global, Inc. - 3</t>
+  </si>
+  <si>
+    <t>MARA Holdings, Inc.</t>
   </si>
   <si>
     <t>Bitcoin USD</t>
   </si>
   <si>
-    <t>Riot Platforms, Inc.</t>
-  </si>
-  <si>
-    <t>MARA Holdings, Inc.</t>
-  </si>
-  <si>
-    <t>Coinbase Global, Inc. - 3</t>
-  </si>
-  <si>
     <t>Strategy Inc</t>
   </si>
   <si>
+    <t>RIOT</t>
+  </si>
+  <si>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>MARA</t>
+  </si>
+  <si>
     <t>BTC-USD</t>
   </si>
   <si>
-    <t>RIOT</t>
-  </si>
-  <si>
-    <t>MARA</t>
-  </si>
-  <si>
-    <t>COIN</t>
-  </si>
-  <si>
     <t>MSTR</t>
   </si>
   <si>
@@ -98,9 +98,6 @@
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
-  </si>
-  <si>
-    <t>🤏 바닥권 접근 구간입니다.</t>
   </si>
   <si>
     <t>⚪ 중립 구간</t>
@@ -522,13 +519,13 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>91215.8</v>
+        <v>14.98</v>
       </c>
       <c r="E2">
-        <v>64.40000000000001</v>
+        <v>59.2</v>
       </c>
       <c r="F2">
-        <v>3.15</v>
+        <v>13.4</v>
       </c>
       <c r="G2">
         <v>50</v>
@@ -537,13 +534,13 @@
         <v>50</v>
       </c>
       <c r="I2">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J2">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="K2">
-        <v>48.7</v>
+        <v>52.5</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -552,10 +549,10 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -569,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>14.16</v>
+        <v>250.56</v>
       </c>
       <c r="E3">
-        <v>40.2</v>
+        <v>50.1</v>
       </c>
       <c r="F3">
-        <v>1.72</v>
+        <v>7.18</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H3">
+        <v>66</v>
+      </c>
+      <c r="I3">
         <v>56</v>
       </c>
-      <c r="I3">
-        <v>50</v>
-      </c>
       <c r="J3">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="K3">
-        <v>44.5</v>
+        <v>50.9</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -599,10 +596,10 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -616,19 +613,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>9.91</v>
+        <v>10.31</v>
       </c>
       <c r="E4">
-        <v>30.4</v>
+        <v>45.9</v>
       </c>
       <c r="F4">
-        <v>-0.3</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G4">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H4">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I4">
         <v>60</v>
@@ -637,7 +634,7 @@
         <v>66</v>
       </c>
       <c r="K4">
-        <v>42.5</v>
+        <v>49.5</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -646,10 +643,10 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -663,40 +660,40 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>236.53</v>
+        <v>92361.59</v>
       </c>
       <c r="E5">
-        <v>28.4</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F5">
-        <v>-1.33</v>
+        <v>4.09</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H5">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="I5">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="J5">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="K5">
-        <v>37.9</v>
+        <v>46.9</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
       </c>
       <c r="M5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5">
+        <v>45.04298008974126</v>
+      </c>
+      <c r="O5" t="s">
         <v>28</v>
-      </c>
-      <c r="N5">
-        <v>41.50472307187444</v>
-      </c>
-      <c r="O5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -710,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>157.16</v>
+        <v>157.97</v>
       </c>
       <c r="E6">
-        <v>29.2</v>
+        <v>46.3</v>
       </c>
       <c r="F6">
-        <v>-0.98</v>
+        <v>1.66</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H6">
+        <v>30</v>
+      </c>
+      <c r="I6">
         <v>43</v>
       </c>
-      <c r="I6">
-        <v>46</v>
-      </c>
       <c r="J6">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K6">
-        <v>36.9</v>
+        <v>42.7</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -740,10 +737,10 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -540,7 +540,7 @@
         <v>56</v>
       </c>
       <c r="K2">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -587,7 +587,7 @@
         <v>53</v>
       </c>
       <c r="K3">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -634,7 +634,7 @@
         <v>66</v>
       </c>
       <c r="K4">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,19 +660,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>92361.59</v>
+        <v>92703.09</v>
       </c>
       <c r="E5">
-        <v>70.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="F5">
-        <v>4.09</v>
+        <v>4.48</v>
       </c>
       <c r="G5">
         <v>50</v>
       </c>
       <c r="H5">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I5">
         <v>46</v>
@@ -681,7 +681,7 @@
         <v>36</v>
       </c>
       <c r="K5">
-        <v>46.9</v>
+        <v>47</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -728,7 +728,7 @@
         <v>53</v>
       </c>
       <c r="K6">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -61,37 +61,37 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-07</t>
+    <t>2026-01-08</t>
   </si>
   <si>
     <t>Riot Platforms, Inc.</t>
   </si>
   <si>
+    <t>MARA Holdings, Inc.</t>
+  </si>
+  <si>
     <t>Coinbase Global, Inc. - 3</t>
   </si>
   <si>
-    <t>MARA Holdings, Inc.</t>
+    <t>Strategy Inc</t>
   </si>
   <si>
     <t>Bitcoin USD</t>
   </si>
   <si>
-    <t>Strategy Inc</t>
-  </si>
-  <si>
     <t>RIOT</t>
   </si>
   <si>
+    <t>MARA</t>
+  </si>
+  <si>
     <t>COIN</t>
   </si>
   <si>
-    <t>MARA</t>
+    <t>MSTR</t>
   </si>
   <si>
     <t>BTC-USD</t>
-  </si>
-  <si>
-    <t>MSTR</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>14.98</v>
+        <v>15.27</v>
       </c>
       <c r="E2">
-        <v>59.2</v>
+        <v>62.9</v>
       </c>
       <c r="F2">
-        <v>13.4</v>
+        <v>20.24</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H2">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I2">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J2">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="K2">
-        <v>52.6</v>
+        <v>57.5</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>250.56</v>
+        <v>10.08</v>
       </c>
       <c r="E3">
-        <v>50.1</v>
+        <v>43.9</v>
       </c>
       <c r="F3">
-        <v>7.18</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H3">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="I3">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="J3">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="K3">
-        <v>51</v>
+        <v>50.3</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>10.31</v>
+        <v>245.93</v>
       </c>
       <c r="E4">
         <v>45.9</v>
       </c>
       <c r="F4">
-        <v>8.640000000000001</v>
+        <v>6.19</v>
       </c>
       <c r="G4">
         <v>40</v>
       </c>
       <c r="H4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I4">
         <v>60</v>
       </c>
       <c r="J4">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="K4">
-        <v>49.6</v>
+        <v>49.1</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>92703.09</v>
+        <v>161.83</v>
       </c>
       <c r="E5">
-        <v>72.7</v>
+        <v>44.8</v>
       </c>
       <c r="F5">
-        <v>4.48</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H5">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I5">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="J5">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="K5">
-        <v>47</v>
+        <v>46.3</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>157.97</v>
+        <v>90038.71000000001</v>
       </c>
       <c r="E6">
-        <v>46.3</v>
+        <v>60.2</v>
       </c>
       <c r="F6">
-        <v>1.66</v>
+        <v>-0.62</v>
       </c>
       <c r="G6">
+        <v>50</v>
+      </c>
+      <c r="H6">
+        <v>33</v>
+      </c>
+      <c r="I6">
         <v>40</v>
       </c>
-      <c r="H6">
-        <v>30</v>
-      </c>
-      <c r="I6">
+      <c r="J6">
         <v>43</v>
       </c>
-      <c r="J6">
-        <v>53</v>
-      </c>
       <c r="K6">
-        <v>42.8</v>
+        <v>44.1</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
   <si>
     <t>날짜</t>
   </si>
@@ -61,13 +61,16 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-08</t>
+    <t>2026-01-11</t>
+  </si>
+  <si>
+    <t>MARA Holdings, Inc.</t>
   </si>
   <si>
     <t>Riot Platforms, Inc.</t>
   </si>
   <si>
-    <t>MARA Holdings, Inc.</t>
+    <t>Bitcoin USD</t>
   </si>
   <si>
     <t>Coinbase Global, Inc. - 3</t>
@@ -76,13 +79,13 @@
     <t>Strategy Inc</t>
   </si>
   <si>
-    <t>Bitcoin USD</t>
+    <t>MARA</t>
   </si>
   <si>
     <t>RIOT</t>
   </si>
   <si>
-    <t>MARA</t>
+    <t>BTC-USD</t>
   </si>
   <si>
     <t>COIN</t>
@@ -91,10 +94,10 @@
     <t>MSTR</t>
   </si>
   <si>
-    <t>BTC-USD</t>
-  </si>
-  <si>
     <t>Pattern</t>
+  </si>
+  <si>
+    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -519,28 +522,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>15.27</v>
+        <v>10.22</v>
       </c>
       <c r="E2">
-        <v>62.9</v>
+        <v>55.8</v>
       </c>
       <c r="F2">
-        <v>20.24</v>
+        <v>3.13</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="I2">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J2">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K2">
-        <v>57.5</v>
+        <v>61.1</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,10 +552,10 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -566,40 +569,40 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>10.08</v>
+        <v>15.32</v>
       </c>
       <c r="E3">
-        <v>43.9</v>
+        <v>65.2</v>
       </c>
       <c r="F3">
-        <v>8.039999999999999</v>
+        <v>8.19</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H3">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="I3">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J3">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="K3">
-        <v>50.3</v>
+        <v>57.1</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
       </c>
       <c r="M3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N3">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -613,40 +616,40 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>245.93</v>
+        <v>90601.14</v>
       </c>
       <c r="E4">
-        <v>45.9</v>
+        <v>60.6</v>
       </c>
       <c r="F4">
-        <v>6.19</v>
+        <v>-3.34</v>
       </c>
       <c r="G4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H4">
         <v>50</v>
       </c>
       <c r="I4">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J4">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="K4">
-        <v>49.1</v>
+        <v>51.3</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
       </c>
       <c r="M4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N4">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -660,40 +663,40 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>161.83</v>
+        <v>240.78</v>
       </c>
       <c r="E5">
-        <v>44.8</v>
+        <v>51.1</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="G5">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H5">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I5">
         <v>53</v>
       </c>
       <c r="J5">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K5">
-        <v>46.3</v>
+        <v>51.3</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
       </c>
       <c r="M5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N5">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -707,40 +710,40 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>90038.71000000001</v>
+        <v>157.33</v>
       </c>
       <c r="E6">
-        <v>60.2</v>
+        <v>49.2</v>
       </c>
       <c r="F6">
-        <v>-0.62</v>
+        <v>0.11</v>
       </c>
       <c r="G6">
+        <v>40</v>
+      </c>
+      <c r="H6">
         <v>50</v>
       </c>
-      <c r="H6">
-        <v>33</v>
-      </c>
       <c r="I6">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J6">
         <v>43</v>
       </c>
       <c r="K6">
-        <v>44.1</v>
+        <v>47.1</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
       </c>
       <c r="M6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N6">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -616,7 +616,7 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>90601.14</v>
+        <v>90598.46000000001</v>
       </c>
       <c r="E4">
         <v>60.6</v>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-11</t>
+    <t>2026-01-12</t>
   </si>
   <si>
     <t>MARA Holdings, Inc.</t>
@@ -70,12 +70,12 @@
     <t>Riot Platforms, Inc.</t>
   </si>
   <si>
+    <t>Coinbase Global, Inc. - 3</t>
+  </si>
+  <si>
     <t>Bitcoin USD</t>
   </si>
   <si>
-    <t>Coinbase Global, Inc. - 3</t>
-  </si>
-  <si>
     <t>Strategy Inc</t>
   </si>
   <si>
@@ -85,10 +85,10 @@
     <t>RIOT</t>
   </si>
   <si>
+    <t>COIN</t>
+  </si>
+  <si>
     <t>BTC-USD</t>
-  </si>
-  <si>
-    <t>COIN</t>
   </si>
   <si>
     <t>MSTR</t>
@@ -552,7 +552,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O2" t="s">
         <v>29</v>
@@ -599,7 +599,7 @@
         <v>28</v>
       </c>
       <c r="N3">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O3" t="s">
         <v>29</v>
@@ -616,25 +616,25 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>90598.46000000001</v>
+        <v>240.78</v>
       </c>
       <c r="E4">
-        <v>60.6</v>
+        <v>51.1</v>
       </c>
       <c r="F4">
-        <v>-3.34</v>
+        <v>1.8</v>
       </c>
       <c r="G4">
         <v>50</v>
       </c>
       <c r="H4">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="I4">
         <v>53</v>
       </c>
       <c r="J4">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K4">
         <v>51.3</v>
@@ -646,7 +646,7 @@
         <v>28</v>
       </c>
       <c r="N4">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O4" t="s">
         <v>29</v>
@@ -663,28 +663,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>240.78</v>
+        <v>91345.48</v>
       </c>
       <c r="E5">
-        <v>51.1</v>
+        <v>62.8</v>
       </c>
       <c r="F5">
-        <v>1.8</v>
+        <v>-2.54</v>
       </c>
       <c r="G5">
         <v>50</v>
       </c>
       <c r="H5">
+        <v>36</v>
+      </c>
+      <c r="I5">
+        <v>43</v>
+      </c>
+      <c r="J5">
         <v>56</v>
       </c>
-      <c r="I5">
-        <v>53</v>
-      </c>
-      <c r="J5">
-        <v>60</v>
-      </c>
       <c r="K5">
-        <v>51.3</v>
+        <v>47.3</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -693,7 +693,7 @@
         <v>28</v>
       </c>
       <c r="N5">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O5" t="s">
         <v>29</v>
@@ -740,7 +740,7 @@
         <v>28</v>
       </c>
       <c r="N6">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O6" t="s">
         <v>29</v>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -70,12 +70,12 @@
     <t>Riot Platforms, Inc.</t>
   </si>
   <si>
+    <t>Bitcoin USD</t>
+  </si>
+  <si>
     <t>Coinbase Global, Inc. - 3</t>
   </si>
   <si>
-    <t>Bitcoin USD</t>
-  </si>
-  <si>
     <t>Strategy Inc</t>
   </si>
   <si>
@@ -85,10 +85,10 @@
     <t>RIOT</t>
   </si>
   <si>
+    <t>BTC-USD</t>
+  </si>
+  <si>
     <t>COIN</t>
-  </si>
-  <si>
-    <t>BTC-USD</t>
   </si>
   <si>
     <t>MSTR</t>
@@ -543,7 +543,7 @@
         <v>70</v>
       </c>
       <c r="K2">
-        <v>61.1</v>
+        <v>61.2</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -552,7 +552,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O2" t="s">
         <v>29</v>
@@ -590,7 +590,7 @@
         <v>60</v>
       </c>
       <c r="K3">
-        <v>57.1</v>
+        <v>57.2</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -599,7 +599,7 @@
         <v>28</v>
       </c>
       <c r="N3">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O3" t="s">
         <v>29</v>
@@ -616,28 +616,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>240.78</v>
+        <v>91661.46000000001</v>
       </c>
       <c r="E4">
-        <v>51.1</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F4">
-        <v>1.8</v>
+        <v>0.39</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H4">
+        <v>53</v>
+      </c>
+      <c r="I4">
         <v>56</v>
       </c>
-      <c r="I4">
-        <v>53</v>
-      </c>
       <c r="J4">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K4">
-        <v>51.3</v>
+        <v>55.6</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -646,7 +646,7 @@
         <v>28</v>
       </c>
       <c r="N4">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O4" t="s">
         <v>29</v>
@@ -663,28 +663,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>91345.48</v>
+        <v>240.78</v>
       </c>
       <c r="E5">
-        <v>62.8</v>
+        <v>51.1</v>
       </c>
       <c r="F5">
-        <v>-2.54</v>
+        <v>1.8</v>
       </c>
       <c r="G5">
         <v>50</v>
       </c>
       <c r="H5">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="I5">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="J5">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K5">
-        <v>47.3</v>
+        <v>51.4</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -693,7 +693,7 @@
         <v>28</v>
       </c>
       <c r="N5">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O5" t="s">
         <v>29</v>
@@ -731,7 +731,7 @@
         <v>43</v>
       </c>
       <c r="K6">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -740,7 +740,7 @@
         <v>28</v>
       </c>
       <c r="N6">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O6" t="s">
         <v>29</v>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
   <si>
     <t>날짜</t>
   </si>
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-12</t>
+    <t>2026-01-13</t>
   </si>
   <si>
     <t>MARA Holdings, Inc.</t>
@@ -95,9 +95,6 @@
   </si>
   <si>
     <t>Pattern</t>
-  </si>
-  <si>
-    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -522,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>10.22</v>
+        <v>10.65</v>
       </c>
       <c r="E2">
-        <v>55.8</v>
+        <v>55.2</v>
       </c>
       <c r="F2">
-        <v>3.13</v>
+        <v>0.57</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I2">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="J2">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="K2">
-        <v>61.2</v>
+        <v>57.6</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -552,10 +549,10 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>50.56766494832259</v>
+        <v>47.98314273412904</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -569,40 +566,40 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>15.32</v>
+        <v>16.45</v>
       </c>
       <c r="E3">
-        <v>65.2</v>
+        <v>65.3</v>
       </c>
       <c r="F3">
-        <v>8.19</v>
+        <v>11.22</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I3">
         <v>60</v>
       </c>
       <c r="J3">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K3">
-        <v>57.2</v>
+        <v>53.4</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
       </c>
       <c r="M3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3">
+        <v>47.98314273412904</v>
+      </c>
+      <c r="O3" t="s">
         <v>28</v>
-      </c>
-      <c r="N3">
-        <v>50.56766494832259</v>
-      </c>
-      <c r="O3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -616,40 +613,40 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>91661.46000000001</v>
+        <v>91251.46000000001</v>
       </c>
       <c r="E4">
-        <v>66.90000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F4">
-        <v>0.39</v>
+        <v>-0.06</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H4">
         <v>53</v>
       </c>
       <c r="I4">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J4">
         <v>63</v>
       </c>
       <c r="K4">
-        <v>55.6</v>
+        <v>50.6</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
       </c>
       <c r="M4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4">
+        <v>47.98314273412904</v>
+      </c>
+      <c r="O4" t="s">
         <v>28</v>
-      </c>
-      <c r="N4">
-        <v>50.56766494832259</v>
-      </c>
-      <c r="O4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -663,40 +660,40 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>240.78</v>
+        <v>242.98</v>
       </c>
       <c r="E5">
-        <v>51.1</v>
+        <v>48.5</v>
       </c>
       <c r="F5">
-        <v>1.8</v>
+        <v>-4.68</v>
       </c>
       <c r="G5">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H5">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="I5">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J5">
         <v>60</v>
       </c>
       <c r="K5">
-        <v>51.4</v>
+        <v>50.4</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
       </c>
       <c r="M5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5">
+        <v>47.98314273412904</v>
+      </c>
+      <c r="O5" t="s">
         <v>28</v>
-      </c>
-      <c r="N5">
-        <v>50.56766494832259</v>
-      </c>
-      <c r="O5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -710,40 +707,40 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>157.33</v>
+        <v>162.23</v>
       </c>
       <c r="E6">
-        <v>49.2</v>
+        <v>47.8</v>
       </c>
       <c r="F6">
-        <v>0.11</v>
+        <v>-1.51</v>
       </c>
       <c r="G6">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H6">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I6">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="J6">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="K6">
-        <v>47.2</v>
+        <v>47.8</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
       </c>
       <c r="M6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6">
+        <v>47.98314273412904</v>
+      </c>
+      <c r="O6" t="s">
         <v>28</v>
-      </c>
-      <c r="N6">
-        <v>50.56766494832259</v>
-      </c>
-      <c r="O6" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -61,7 +61,10 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-13</t>
+    <t>2026-01-14</t>
+  </si>
+  <si>
+    <t>Coinbase Global, Inc. - 3</t>
   </si>
   <si>
     <t>MARA Holdings, Inc.</t>
@@ -73,12 +76,12 @@
     <t>Bitcoin USD</t>
   </si>
   <si>
-    <t>Coinbase Global, Inc. - 3</t>
-  </si>
-  <si>
     <t>Strategy Inc</t>
   </si>
   <si>
+    <t>COIN</t>
+  </si>
+  <si>
     <t>MARA</t>
   </si>
   <si>
@@ -86,9 +89,6 @@
   </si>
   <si>
     <t>BTC-USD</t>
-  </si>
-  <si>
-    <t>COIN</t>
   </si>
   <si>
     <t>MSTR</t>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>10.65</v>
+        <v>252.69</v>
       </c>
       <c r="E2">
-        <v>55.2</v>
+        <v>53.1</v>
       </c>
       <c r="F2">
-        <v>0.57</v>
+        <v>0.85</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I2">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="J2">
         <v>66</v>
       </c>
       <c r="K2">
-        <v>57.6</v>
+        <v>58.9</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>16.45</v>
+        <v>10.95</v>
       </c>
       <c r="E3">
-        <v>65.3</v>
+        <v>58.6</v>
       </c>
       <c r="F3">
-        <v>11.22</v>
+        <v>6.21</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I3">
         <v>60</v>
       </c>
       <c r="J3">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="K3">
-        <v>53.4</v>
+        <v>54.9</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>91251.46000000001</v>
+        <v>16.75</v>
       </c>
       <c r="E4">
-        <v>65.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="F4">
-        <v>-0.06</v>
+        <v>11.82</v>
       </c>
       <c r="G4">
         <v>50</v>
       </c>
       <c r="H4">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="I4">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="J4">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K4">
-        <v>50.6</v>
+        <v>54.3</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>242.98</v>
+        <v>94975.45</v>
       </c>
       <c r="E5">
-        <v>48.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F5">
-        <v>-4.68</v>
+        <v>4.93</v>
       </c>
       <c r="G5">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H5">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="I5">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J5">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="K5">
-        <v>50.4</v>
+        <v>53.1</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>162.23</v>
+        <v>172.99</v>
       </c>
       <c r="E6">
-        <v>47.8</v>
+        <v>56.3</v>
       </c>
       <c r="F6">
-        <v>-1.51</v>
+        <v>9.51</v>
       </c>
       <c r="G6">
         <v>50</v>
       </c>
       <c r="H6">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="I6">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="J6">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K6">
-        <v>47.8</v>
+        <v>42.3</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -61,37 +61,37 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-14</t>
+    <t>2026-01-17</t>
+  </si>
+  <si>
+    <t>MARA Holdings, Inc.</t>
+  </si>
+  <si>
+    <t>Riot Platforms, Inc.</t>
+  </si>
+  <si>
+    <t>Bitcoin USD</t>
+  </si>
+  <si>
+    <t>Strategy Inc</t>
   </si>
   <si>
     <t>Coinbase Global, Inc. - 3</t>
   </si>
   <si>
-    <t>MARA Holdings, Inc.</t>
-  </si>
-  <si>
-    <t>Riot Platforms, Inc.</t>
-  </si>
-  <si>
-    <t>Bitcoin USD</t>
-  </si>
-  <si>
-    <t>Strategy Inc</t>
+    <t>MARA</t>
+  </si>
+  <si>
+    <t>RIOT</t>
+  </si>
+  <si>
+    <t>BTC-USD</t>
+  </si>
+  <si>
+    <t>MSTR</t>
   </si>
   <si>
     <t>COIN</t>
-  </si>
-  <si>
-    <t>MARA</t>
-  </si>
-  <si>
-    <t>RIOT</t>
-  </si>
-  <si>
-    <t>BTC-USD</t>
-  </si>
-  <si>
-    <t>MSTR</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -519,13 +519,13 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>252.69</v>
+        <v>11.36</v>
       </c>
       <c r="E2">
-        <v>53.1</v>
+        <v>66.5</v>
       </c>
       <c r="F2">
-        <v>0.85</v>
+        <v>11.15</v>
       </c>
       <c r="G2">
         <v>60</v>
@@ -534,13 +534,13 @@
         <v>56</v>
       </c>
       <c r="I2">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="J2">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="K2">
-        <v>58.9</v>
+        <v>54.1</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>10.95</v>
+        <v>19.24</v>
       </c>
       <c r="E3">
-        <v>58.6</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="F3">
-        <v>6.21</v>
+        <v>25.59</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H3">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="I3">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J3">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="K3">
-        <v>54.9</v>
+        <v>53.3</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>16.75</v>
+        <v>95225.25</v>
       </c>
       <c r="E4">
-        <v>67.8</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F4">
-        <v>11.82</v>
+        <v>4.42</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H4">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="I4">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="J4">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="K4">
-        <v>54.3</v>
+        <v>52.5</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>94975.45</v>
+        <v>173.71</v>
       </c>
       <c r="E5">
-        <v>74.59999999999999</v>
+        <v>59.5</v>
       </c>
       <c r="F5">
-        <v>4.93</v>
+        <v>10.41</v>
       </c>
       <c r="G5">
+        <v>60</v>
+      </c>
+      <c r="H5">
+        <v>40</v>
+      </c>
+      <c r="I5">
         <v>50</v>
       </c>
-      <c r="H5">
-        <v>60</v>
-      </c>
-      <c r="I5">
-        <v>63</v>
-      </c>
       <c r="J5">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="K5">
-        <v>53.1</v>
+        <v>50.1</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>172.99</v>
+        <v>241.15</v>
       </c>
       <c r="E6">
-        <v>56.3</v>
+        <v>52.4</v>
       </c>
       <c r="F6">
-        <v>9.51</v>
+        <v>0.15</v>
       </c>
       <c r="G6">
         <v>50</v>
       </c>
       <c r="H6">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I6">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J6">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="K6">
-        <v>42.3</v>
+        <v>48.3</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -613,13 +613,13 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>95225.25</v>
+        <v>95145.28999999999</v>
       </c>
       <c r="E4">
-        <v>65.40000000000001</v>
+        <v>65</v>
       </c>
       <c r="F4">
-        <v>4.42</v>
+        <v>4.33</v>
       </c>
       <c r="G4">
         <v>60</v>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-17</t>
+    <t>2026-01-19</t>
   </si>
   <si>
     <t>MARA Holdings, Inc.</t>
@@ -70,12 +70,12 @@
     <t>Riot Platforms, Inc.</t>
   </si>
   <si>
+    <t>Strategy Inc</t>
+  </si>
+  <si>
     <t>Bitcoin USD</t>
   </si>
   <si>
-    <t>Strategy Inc</t>
-  </si>
-  <si>
     <t>Coinbase Global, Inc. - 3</t>
   </si>
   <si>
@@ -85,10 +85,10 @@
     <t>RIOT</t>
   </si>
   <si>
+    <t>MSTR</t>
+  </si>
+  <si>
     <t>BTC-USD</t>
-  </si>
-  <si>
-    <t>MSTR</t>
   </si>
   <si>
     <t>COIN</t>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>95145.28999999999</v>
+        <v>173.71</v>
       </c>
       <c r="E4">
-        <v>65</v>
+        <v>59.5</v>
       </c>
       <c r="F4">
-        <v>4.33</v>
+        <v>10.41</v>
       </c>
       <c r="G4">
         <v>60</v>
       </c>
       <c r="H4">
+        <v>40</v>
+      </c>
+      <c r="I4">
+        <v>50</v>
+      </c>
+      <c r="J4">
         <v>43</v>
       </c>
-      <c r="I4">
-        <v>56</v>
-      </c>
-      <c r="J4">
-        <v>56</v>
-      </c>
       <c r="K4">
-        <v>52.5</v>
+        <v>50.1</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>173.71</v>
+        <v>92558.8</v>
       </c>
       <c r="E5">
-        <v>59.5</v>
+        <v>45.4</v>
       </c>
       <c r="F5">
-        <v>10.41</v>
+        <v>-4.51</v>
       </c>
       <c r="G5">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H5">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I5">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J5">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="K5">
-        <v>50.1</v>
+        <v>49.5</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-19</t>
+    <t>2026-03-03</t>
   </si>
   <si>
     <t>MARA Holdings, Inc.</t>
@@ -73,12 +73,12 @@
     <t>Strategy Inc</t>
   </si>
   <si>
+    <t>Coinbase Global, Inc. - 3</t>
+  </si>
+  <si>
     <t>Bitcoin USD</t>
   </si>
   <si>
-    <t>Coinbase Global, Inc. - 3</t>
-  </si>
-  <si>
     <t>MARA</t>
   </si>
   <si>
@@ -88,19 +88,19 @@
     <t>MSTR</t>
   </si>
   <si>
+    <t>COIN</t>
+  </si>
+  <si>
     <t>BTC-USD</t>
   </si>
   <si>
-    <t>COIN</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>⚪ 중립 구간</t>
+    <t>🔴 강한 긴축 / 리스크</t>
   </si>
 </sst>
 </file>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>11.36</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="E2">
-        <v>66.5</v>
+        <v>66.3</v>
       </c>
       <c r="F2">
-        <v>11.15</v>
+        <v>19.92</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I2">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J2">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="K2">
-        <v>54.1</v>
+        <v>45.3</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>19.24</v>
+        <v>16.43</v>
       </c>
       <c r="E3">
-        <v>81.90000000000001</v>
+        <v>60.6</v>
       </c>
       <c r="F3">
-        <v>25.59</v>
+        <v>4.98</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H3">
+        <v>50</v>
+      </c>
+      <c r="I3">
         <v>53</v>
       </c>
-      <c r="I3">
-        <v>73</v>
-      </c>
       <c r="J3">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="K3">
-        <v>53.3</v>
+        <v>45.3</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>173.71</v>
+        <v>137.65</v>
       </c>
       <c r="E4">
-        <v>59.5</v>
+        <v>49.5</v>
       </c>
       <c r="F4">
-        <v>10.41</v>
+        <v>11.27</v>
       </c>
       <c r="G4">
         <v>60</v>
       </c>
       <c r="H4">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I4">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="J4">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="K4">
-        <v>50.1</v>
+        <v>41.3</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>92558.8</v>
+        <v>185.24</v>
       </c>
       <c r="E5">
-        <v>45.4</v>
+        <v>58</v>
       </c>
       <c r="F5">
-        <v>-4.51</v>
+        <v>15.6</v>
       </c>
       <c r="G5">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H5">
+        <v>40</v>
+      </c>
+      <c r="I5">
+        <v>36</v>
+      </c>
+      <c r="J5">
         <v>46</v>
       </c>
-      <c r="I5">
-        <v>56</v>
-      </c>
-      <c r="J5">
-        <v>63</v>
-      </c>
       <c r="K5">
-        <v>49.5</v>
+        <v>38.5</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>241.15</v>
+        <v>66834.66</v>
       </c>
       <c r="E6">
-        <v>52.4</v>
+        <v>48.3</v>
       </c>
       <c r="F6">
-        <v>0.15</v>
+        <v>-0.92</v>
       </c>
       <c r="G6">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H6">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I6">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="J6">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="K6">
-        <v>48.3</v>
+        <v>33.5</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
   <si>
     <t>날짜</t>
   </si>
@@ -61,43 +61,46 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-03</t>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>Strategy Inc</t>
+  </si>
+  <si>
+    <t>Coinbase Global, Inc. - 3</t>
+  </si>
+  <si>
+    <t>Bitcoin USD</t>
+  </si>
+  <si>
+    <t>Riot Platforms, Inc.</t>
   </si>
   <si>
     <t>MARA Holdings, Inc.</t>
   </si>
   <si>
-    <t>Riot Platforms, Inc.</t>
-  </si>
-  <si>
-    <t>Strategy Inc</t>
-  </si>
-  <si>
-    <t>Coinbase Global, Inc. - 3</t>
-  </si>
-  <si>
-    <t>Bitcoin USD</t>
+    <t>MSTR</t>
+  </si>
+  <si>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>BTC-USD</t>
+  </si>
+  <si>
+    <t>RIOT</t>
   </si>
   <si>
     <t>MARA</t>
   </si>
   <si>
-    <t>RIOT</t>
-  </si>
-  <si>
-    <t>MSTR</t>
-  </si>
-  <si>
-    <t>COIN</t>
-  </si>
-  <si>
-    <t>BTC-USD</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
+  </si>
+  <si>
+    <t>🤏 바닥권 접근 구간입니다.</t>
   </si>
   <si>
     <t>🔴 강한 긴축 / 리스크</t>
@@ -519,28 +522,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>9.449999999999999</v>
+        <v>133.53</v>
       </c>
       <c r="E2">
-        <v>66.3</v>
+        <v>49.8</v>
       </c>
       <c r="F2">
-        <v>19.92</v>
+        <v>3.11</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="I2">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="J2">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K2">
-        <v>45.3</v>
+        <v>37.7</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,10 +552,10 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -566,28 +569,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>16.43</v>
+        <v>197.22</v>
       </c>
       <c r="E3">
-        <v>60.6</v>
+        <v>65.8</v>
       </c>
       <c r="F3">
-        <v>4.98</v>
+        <v>12.15</v>
       </c>
       <c r="G3">
         <v>60</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="I3">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="J3">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="K3">
-        <v>45.3</v>
+        <v>33.7</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,10 +599,10 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -613,28 +616,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>137.65</v>
+        <v>66342.91</v>
       </c>
       <c r="E4">
-        <v>49.5</v>
+        <v>47.5</v>
       </c>
       <c r="F4">
-        <v>11.27</v>
+        <v>-2.86</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H4">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="I4">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="J4">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="K4">
-        <v>41.3</v>
+        <v>33.3</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,10 +646,10 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -660,40 +663,40 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>185.24</v>
+        <v>14.16</v>
       </c>
       <c r="E5">
-        <v>58</v>
+        <v>44.6</v>
       </c>
       <c r="F5">
-        <v>15.6</v>
+        <v>-13.04</v>
       </c>
       <c r="G5">
+        <v>30</v>
+      </c>
+      <c r="H5">
         <v>60</v>
       </c>
-      <c r="H5">
-        <v>40</v>
-      </c>
       <c r="I5">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J5">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="K5">
-        <v>38.5</v>
+        <v>31.5</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
       </c>
       <c r="M5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N5">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -707,28 +710,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>66834.66</v>
+        <v>8.01</v>
       </c>
       <c r="E6">
-        <v>48.3</v>
+        <v>50.8</v>
       </c>
       <c r="F6">
-        <v>-0.92</v>
+        <v>-10.4</v>
       </c>
       <c r="G6">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H6">
+        <v>43</v>
+      </c>
+      <c r="I6">
+        <v>40</v>
+      </c>
+      <c r="J6">
         <v>53</v>
       </c>
-      <c r="I6">
-        <v>46</v>
-      </c>
-      <c r="J6">
-        <v>33</v>
-      </c>
       <c r="K6">
-        <v>33.5</v>
+        <v>29.3</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,10 +740,10 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -64,28 +64,28 @@
     <t>2026-03-09</t>
   </si>
   <si>
+    <t>Bitcoin USD</t>
+  </si>
+  <si>
     <t>Strategy Inc</t>
   </si>
   <si>
     <t>Coinbase Global, Inc. - 3</t>
   </si>
   <si>
-    <t>Bitcoin USD</t>
-  </si>
-  <si>
     <t>Riot Platforms, Inc.</t>
   </si>
   <si>
     <t>MARA Holdings, Inc.</t>
   </si>
   <si>
+    <t>BTC-USD</t>
+  </si>
+  <si>
     <t>MSTR</t>
   </si>
   <si>
     <t>COIN</t>
-  </si>
-  <si>
-    <t>BTC-USD</t>
   </si>
   <si>
     <t>RIOT</t>
@@ -522,28 +522,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>133.53</v>
+        <v>67509.72</v>
       </c>
       <c r="E2">
-        <v>49.8</v>
+        <v>55.8</v>
       </c>
       <c r="F2">
-        <v>3.11</v>
+        <v>-7.15</v>
       </c>
       <c r="G2">
+        <v>50</v>
+      </c>
+      <c r="H2">
+        <v>50</v>
+      </c>
+      <c r="I2">
         <v>60</v>
       </c>
-      <c r="H2">
-        <v>40</v>
-      </c>
-      <c r="I2">
-        <v>46</v>
-      </c>
       <c r="J2">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="K2">
-        <v>37.7</v>
+        <v>39</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -552,7 +552,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O2" t="s">
         <v>29</v>
@@ -569,28 +569,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>197.22</v>
+        <v>133.53</v>
       </c>
       <c r="E3">
-        <v>65.8</v>
+        <v>49.8</v>
       </c>
       <c r="F3">
-        <v>12.15</v>
+        <v>3.11</v>
       </c>
       <c r="G3">
         <v>60</v>
       </c>
       <c r="H3">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I3">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="J3">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K3">
-        <v>33.7</v>
+        <v>36.4</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -599,7 +599,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O3" t="s">
         <v>29</v>
@@ -616,28 +616,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>66342.91</v>
+        <v>197.22</v>
       </c>
       <c r="E4">
-        <v>47.5</v>
+        <v>65.8</v>
       </c>
       <c r="F4">
-        <v>-2.86</v>
+        <v>12.15</v>
       </c>
       <c r="G4">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H4">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="I4">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="J4">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="K4">
-        <v>33.3</v>
+        <v>32.4</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -646,7 +646,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O4" t="s">
         <v>29</v>
@@ -684,7 +684,7 @@
         <v>70</v>
       </c>
       <c r="K5">
-        <v>31.5</v>
+        <v>30.2</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -693,7 +693,7 @@
         <v>28</v>
       </c>
       <c r="N5">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O5" t="s">
         <v>29</v>
@@ -731,7 +731,7 @@
         <v>53</v>
       </c>
       <c r="K6">
-        <v>29.3</v>
+        <v>28</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -740,7 +740,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O6" t="s">
         <v>29</v>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -61,13 +61,16 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-09</t>
+    <t>2026-03-10</t>
+  </si>
+  <si>
+    <t>Strategy Inc</t>
   </si>
   <si>
     <t>Bitcoin USD</t>
   </si>
   <si>
-    <t>Strategy Inc</t>
+    <t>MARA Holdings, Inc.</t>
   </si>
   <si>
     <t>Coinbase Global, Inc. - 3</t>
@@ -76,13 +79,13 @@
     <t>Riot Platforms, Inc.</t>
   </si>
   <si>
-    <t>MARA Holdings, Inc.</t>
+    <t>MSTR</t>
   </si>
   <si>
     <t>BTC-USD</t>
   </si>
   <si>
-    <t>MSTR</t>
+    <t>MARA</t>
   </si>
   <si>
     <t>COIN</t>
@@ -91,9 +94,6 @@
     <t>RIOT</t>
   </si>
   <si>
-    <t>MARA</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
@@ -103,7 +103,7 @@
     <t>🤏 바닥권 접근 구간입니다.</t>
   </si>
   <si>
-    <t>🔴 강한 긴축 / 리스크</t>
+    <t>🟠 하락 우위 (긴장 구간)</t>
   </si>
 </sst>
 </file>
@@ -522,28 +522,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>67509.72</v>
+        <v>138.95</v>
       </c>
       <c r="E2">
-        <v>55.8</v>
+        <v>56.4</v>
       </c>
       <c r="F2">
-        <v>-7.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G2">
+        <v>60</v>
+      </c>
+      <c r="H2">
+        <v>36</v>
+      </c>
+      <c r="I2">
         <v>50</v>
       </c>
-      <c r="H2">
-        <v>50</v>
-      </c>
-      <c r="I2">
-        <v>60</v>
-      </c>
       <c r="J2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K2">
-        <v>39</v>
+        <v>47.7</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -552,7 +552,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O2" t="s">
         <v>29</v>
@@ -569,28 +569,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>133.53</v>
+        <v>69785.31</v>
       </c>
       <c r="E3">
-        <v>49.8</v>
+        <v>59.4</v>
       </c>
       <c r="F3">
-        <v>3.11</v>
+        <v>-4.02</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I3">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="J3">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="K3">
-        <v>36.4</v>
+        <v>47.1</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -599,7 +599,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O3" t="s">
         <v>29</v>
@@ -616,28 +616,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>197.22</v>
+        <v>8.66</v>
       </c>
       <c r="E4">
-        <v>65.8</v>
+        <v>60</v>
       </c>
       <c r="F4">
-        <v>12.15</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H4">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="I4">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="J4">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K4">
-        <v>32.4</v>
+        <v>47.1</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -646,7 +646,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O4" t="s">
         <v>29</v>
@@ -663,37 +663,37 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>14.16</v>
+        <v>199.79</v>
       </c>
       <c r="E5">
-        <v>44.6</v>
+        <v>66</v>
       </c>
       <c r="F5">
-        <v>-13.04</v>
+        <v>7.85</v>
       </c>
       <c r="G5">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H5">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I5">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="J5">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="K5">
-        <v>30.2</v>
+        <v>44.9</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
       </c>
       <c r="M5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O5" t="s">
         <v>29</v>
@@ -710,37 +710,37 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>8.01</v>
+        <v>14.7</v>
       </c>
       <c r="E6">
-        <v>50.8</v>
+        <v>50.3</v>
       </c>
       <c r="F6">
-        <v>-10.4</v>
+        <v>-10.53</v>
       </c>
       <c r="G6">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H6">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="I6">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J6">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="K6">
-        <v>28</v>
+        <v>39.7</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
       </c>
       <c r="M6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O6" t="s">
         <v>29</v>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -67,12 +67,12 @@
     <t>Strategy Inc</t>
   </si>
   <si>
+    <t>MARA Holdings, Inc.</t>
+  </si>
+  <si>
     <t>Bitcoin USD</t>
   </si>
   <si>
-    <t>MARA Holdings, Inc.</t>
-  </si>
-  <si>
     <t>Coinbase Global, Inc. - 3</t>
   </si>
   <si>
@@ -82,10 +82,10 @@
     <t>MSTR</t>
   </si>
   <si>
+    <t>MARA</t>
+  </si>
+  <si>
     <t>BTC-USD</t>
-  </si>
-  <si>
-    <t>MARA</t>
   </si>
   <si>
     <t>COIN</t>
@@ -552,7 +552,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O2" t="s">
         <v>29</v>
@@ -569,19 +569,19 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>69785.31</v>
+        <v>8.66</v>
       </c>
       <c r="E3">
-        <v>59.4</v>
+        <v>60</v>
       </c>
       <c r="F3">
-        <v>-4.02</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="G3">
         <v>50</v>
       </c>
       <c r="H3">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="I3">
         <v>56</v>
@@ -599,7 +599,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O3" t="s">
         <v>29</v>
@@ -616,28 +616,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>8.66</v>
+        <v>70051.36</v>
       </c>
       <c r="E4">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F4">
-        <v>-8.359999999999999</v>
+        <v>-1.11</v>
       </c>
       <c r="G4">
         <v>50</v>
       </c>
       <c r="H4">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="I4">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J4">
         <v>50</v>
       </c>
       <c r="K4">
-        <v>47.1</v>
+        <v>45.9</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -646,7 +646,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O4" t="s">
         <v>29</v>
@@ -693,7 +693,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O5" t="s">
         <v>29</v>
@@ -740,7 +740,7 @@
         <v>28</v>
       </c>
       <c r="N6">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O6" t="s">
         <v>29</v>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
   <si>
     <t>날짜</t>
   </si>
@@ -61,49 +61,46 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-10</t>
+    <t>2026-03-11</t>
+  </si>
+  <si>
+    <t>Bitcoin USD</t>
+  </si>
+  <si>
+    <t>Coinbase Global, Inc. - 3</t>
   </si>
   <si>
     <t>Strategy Inc</t>
   </si>
   <si>
+    <t>Riot Platforms, Inc.</t>
+  </si>
+  <si>
     <t>MARA Holdings, Inc.</t>
   </si>
   <si>
-    <t>Bitcoin USD</t>
-  </si>
-  <si>
-    <t>Coinbase Global, Inc. - 3</t>
-  </si>
-  <si>
-    <t>Riot Platforms, Inc.</t>
+    <t>BTC-USD</t>
+  </si>
+  <si>
+    <t>COIN</t>
   </si>
   <si>
     <t>MSTR</t>
   </si>
   <si>
+    <t>RIOT</t>
+  </si>
+  <si>
     <t>MARA</t>
   </si>
   <si>
-    <t>BTC-USD</t>
-  </si>
-  <si>
-    <t>COIN</t>
-  </si>
-  <si>
-    <t>RIOT</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>🤏 바닥권 접근 구간입니다.</t>
-  </si>
-  <si>
-    <t>🟠 하락 우위 (긴장 구간)</t>
+    <t>⚪ 중립 구간</t>
   </si>
 </sst>
 </file>
@@ -522,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>138.95</v>
+        <v>69586.02</v>
       </c>
       <c r="E2">
-        <v>56.4</v>
+        <v>60.3</v>
       </c>
       <c r="F2">
-        <v>0.9399999999999999</v>
+        <v>-1.77</v>
       </c>
       <c r="G2">
+        <v>50</v>
+      </c>
+      <c r="H2">
         <v>60</v>
       </c>
-      <c r="H2">
-        <v>36</v>
-      </c>
       <c r="I2">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J2">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="K2">
-        <v>47.7</v>
+        <v>49.2</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -552,10 +549,10 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -569,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>8.66</v>
+        <v>196.52</v>
       </c>
       <c r="E3">
+        <v>65.2</v>
+      </c>
+      <c r="F3">
+        <v>7.76</v>
+      </c>
+      <c r="G3">
         <v>60</v>
       </c>
-      <c r="F3">
-        <v>-8.359999999999999</v>
-      </c>
-      <c r="G3">
-        <v>50</v>
-      </c>
       <c r="H3">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="I3">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="J3">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K3">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -599,10 +596,10 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -616,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>70051.36</v>
+        <v>138.46</v>
       </c>
       <c r="E4">
-        <v>61</v>
+        <v>58.6</v>
       </c>
       <c r="F4">
-        <v>-1.11</v>
+        <v>4.36</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H4">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="I4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="J4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K4">
-        <v>45.9</v>
+        <v>47</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -646,10 +643,10 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -663,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>199.79</v>
+        <v>14.64</v>
       </c>
       <c r="E5">
+        <v>45.3</v>
+      </c>
+      <c r="F5">
+        <v>-4.25</v>
+      </c>
+      <c r="G5">
+        <v>20</v>
+      </c>
+      <c r="H5">
+        <v>60</v>
+      </c>
+      <c r="I5">
         <v>66</v>
       </c>
-      <c r="F5">
-        <v>7.85</v>
-      </c>
-      <c r="G5">
-        <v>60</v>
-      </c>
-      <c r="H5">
-        <v>46</v>
-      </c>
-      <c r="I5">
-        <v>43</v>
-      </c>
       <c r="J5">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="K5">
-        <v>44.9</v>
+        <v>45.4</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -693,10 +690,10 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -710,40 +707,40 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>14.7</v>
+        <v>8.57</v>
       </c>
       <c r="E6">
-        <v>50.3</v>
+        <v>59.2</v>
       </c>
       <c r="F6">
-        <v>-10.53</v>
+        <v>-1.04</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H6">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I6">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="J6">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="K6">
-        <v>39.7</v>
+        <v>45.2</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
       </c>
       <c r="M6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6">
+        <v>43.44936356612781</v>
+      </c>
+      <c r="O6" t="s">
         <v>28</v>
-      </c>
-      <c r="N6">
-        <v>32.42054265786911</v>
-      </c>
-      <c r="O6" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -61,37 +61,37 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-11</t>
+    <t>2026-03-12</t>
   </si>
   <si>
     <t>Bitcoin USD</t>
   </si>
   <si>
+    <t>MARA Holdings, Inc.</t>
+  </si>
+  <si>
+    <t>Riot Platforms, Inc.</t>
+  </si>
+  <si>
     <t>Coinbase Global, Inc. - 3</t>
   </si>
   <si>
     <t>Strategy Inc</t>
   </si>
   <si>
-    <t>Riot Platforms, Inc.</t>
-  </si>
-  <si>
-    <t>MARA Holdings, Inc.</t>
-  </si>
-  <si>
     <t>BTC-USD</t>
   </si>
   <si>
+    <t>MARA</t>
+  </si>
+  <si>
+    <t>RIOT</t>
+  </si>
+  <si>
     <t>COIN</t>
   </si>
   <si>
     <t>MSTR</t>
-  </si>
-  <si>
-    <t>RIOT</t>
-  </si>
-  <si>
-    <t>MARA</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>69586.02</v>
+        <v>69960.81</v>
       </c>
       <c r="E2">
-        <v>60.3</v>
+        <v>55.4</v>
       </c>
       <c r="F2">
-        <v>-1.77</v>
+        <v>4</v>
       </c>
       <c r="G2">
+        <v>60</v>
+      </c>
+      <c r="H2">
+        <v>56</v>
+      </c>
+      <c r="I2">
+        <v>56</v>
+      </c>
+      <c r="J2">
         <v>50</v>
       </c>
-      <c r="H2">
-        <v>60</v>
-      </c>
-      <c r="I2">
-        <v>53</v>
-      </c>
-      <c r="J2">
-        <v>53</v>
-      </c>
       <c r="K2">
-        <v>49.2</v>
+        <v>52.9</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>43.44936356612781</v>
+        <v>41.74287521812095</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>196.52</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E3">
-        <v>65.2</v>
+        <v>55.5</v>
       </c>
       <c r="F3">
-        <v>7.76</v>
+        <v>-7.97</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H3">
         <v>46</v>
       </c>
       <c r="I3">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J3">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K3">
-        <v>47</v>
+        <v>45.9</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>43.44936356612781</v>
+        <v>41.74287521812095</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>138.46</v>
+        <v>14.81</v>
       </c>
       <c r="E4">
-        <v>58.6</v>
+        <v>41.7</v>
       </c>
       <c r="F4">
-        <v>4.36</v>
+        <v>-10.41</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H4">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I4">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="J4">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="K4">
-        <v>47</v>
+        <v>44.9</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>43.44936356612781</v>
+        <v>41.74287521812095</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>14.64</v>
+        <v>198.63</v>
       </c>
       <c r="E5">
-        <v>45.3</v>
+        <v>65.3</v>
       </c>
       <c r="F5">
-        <v>-4.25</v>
+        <v>-4.93</v>
       </c>
       <c r="G5">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H5">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I5">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="J5">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="K5">
-        <v>45.4</v>
+        <v>44.7</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>43.44936356612781</v>
+        <v>41.74287521812095</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>8.57</v>
+        <v>138.33</v>
       </c>
       <c r="E6">
-        <v>59.2</v>
+        <v>56.1</v>
       </c>
       <c r="F6">
-        <v>-1.04</v>
+        <v>-5.54</v>
       </c>
       <c r="G6">
         <v>50</v>
       </c>
       <c r="H6">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I6">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J6">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K6">
-        <v>45.2</v>
+        <v>40.7</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>43.44936356612781</v>
+        <v>41.74287521812095</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -519,13 +519,13 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>69960.81</v>
+        <v>69976.53</v>
       </c>
       <c r="E2">
-        <v>55.4</v>
+        <v>55.5</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>4.02</v>
       </c>
       <c r="G2">
         <v>60</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
   <si>
     <t>날짜</t>
   </si>
@@ -61,46 +61,49 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-12</t>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>MARA Holdings, Inc.</t>
+  </si>
+  <si>
+    <t>Riot Platforms, Inc.</t>
   </si>
   <si>
     <t>Bitcoin USD</t>
   </si>
   <si>
-    <t>MARA Holdings, Inc.</t>
-  </si>
-  <si>
-    <t>Riot Platforms, Inc.</t>
-  </si>
-  <si>
-    <t>Coinbase Global, Inc. - 3</t>
-  </si>
-  <si>
     <t>Strategy Inc</t>
   </si>
   <si>
+    <t>Coinbase Global, Inc.</t>
+  </si>
+  <si>
+    <t>MARA</t>
+  </si>
+  <si>
+    <t>RIOT</t>
+  </si>
+  <si>
     <t>BTC-USD</t>
   </si>
   <si>
-    <t>MARA</t>
-  </si>
-  <si>
-    <t>RIOT</t>
+    <t>MSTR</t>
   </si>
   <si>
     <t>COIN</t>
   </si>
   <si>
-    <t>MSTR</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
+    <t>📈 매수 관찰 구간입니다.</t>
+  </si>
+  <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>⚪ 중립 구간</t>
+    <t>🟢 상승 우위 (다소 완화)</t>
   </si>
 </sst>
 </file>
@@ -519,28 +522,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>69976.53</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="E2">
-        <v>55.5</v>
+        <v>47.2</v>
       </c>
       <c r="F2">
-        <v>4.02</v>
+        <v>14.87</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I2">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="J2">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="K2">
-        <v>52.9</v>
+        <v>60.2</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,10 +552,10 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -566,28 +569,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>8.550000000000001</v>
+        <v>14.19</v>
       </c>
       <c r="E3">
-        <v>55.5</v>
+        <v>47.3</v>
       </c>
       <c r="F3">
-        <v>-7.97</v>
+        <v>19.95</v>
       </c>
       <c r="G3">
         <v>50</v>
       </c>
       <c r="H3">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="I3">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="J3">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="K3">
-        <v>45.9</v>
+        <v>60.2</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,10 +599,10 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -613,40 +616,40 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>14.81</v>
+        <v>71406.64999999999</v>
       </c>
       <c r="E4">
-        <v>41.7</v>
+        <v>53.1</v>
       </c>
       <c r="F4">
-        <v>-10.41</v>
+        <v>6.75</v>
       </c>
       <c r="G4">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H4">
         <v>46</v>
       </c>
       <c r="I4">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="J4">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="K4">
-        <v>44.9</v>
+        <v>54</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
       </c>
       <c r="M4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N4">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -660,40 +663,40 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>198.63</v>
+        <v>123.72</v>
       </c>
       <c r="E5">
-        <v>65.3</v>
+        <v>27.8</v>
       </c>
       <c r="F5">
-        <v>-4.93</v>
+        <v>1.88</v>
       </c>
       <c r="G5">
+        <v>20</v>
+      </c>
+      <c r="H5">
         <v>50</v>
       </c>
-      <c r="H5">
-        <v>40</v>
-      </c>
       <c r="I5">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="J5">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="K5">
-        <v>44.7</v>
+        <v>47.2</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
       </c>
       <c r="M5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N5">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -707,40 +710,40 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>138.33</v>
+        <v>175.18</v>
       </c>
       <c r="E6">
-        <v>56.1</v>
+        <v>27.5</v>
       </c>
       <c r="F6">
-        <v>-5.54</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G6">
+        <v>20</v>
+      </c>
+      <c r="H6">
+        <v>53</v>
+      </c>
+      <c r="I6">
+        <v>53</v>
+      </c>
+      <c r="J6">
         <v>50</v>
       </c>
-      <c r="H6">
-        <v>46</v>
-      </c>
-      <c r="I6">
-        <v>33</v>
-      </c>
-      <c r="J6">
-        <v>30</v>
-      </c>
       <c r="K6">
-        <v>40.7</v>
+        <v>47.2</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
       </c>
       <c r="M6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N6">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
   <si>
     <t>날짜</t>
   </si>
@@ -61,7 +61,13 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-04-08</t>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>Bitcoin USD</t>
+  </si>
+  <si>
+    <t>Coinbase Global, Inc.</t>
   </si>
   <si>
     <t>MARA Holdings, Inc.</t>
@@ -70,13 +76,13 @@
     <t>Riot Platforms, Inc.</t>
   </si>
   <si>
-    <t>Bitcoin USD</t>
-  </si>
-  <si>
     <t>Strategy Inc</t>
   </si>
   <si>
-    <t>Coinbase Global, Inc.</t>
+    <t>BTC-USD</t>
+  </si>
+  <si>
+    <t>COIN</t>
   </si>
   <si>
     <t>MARA</t>
@@ -85,25 +91,16 @@
     <t>RIOT</t>
   </si>
   <si>
-    <t>BTC-USD</t>
-  </si>
-  <si>
     <t>MSTR</t>
   </si>
   <si>
-    <t>COIN</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
-    <t>📈 매수 관찰 구간입니다.</t>
-  </si>
-  <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>🟢 상승 우위 (다소 완화)</t>
+    <t>⚪ 중립 구간</t>
   </si>
 </sst>
 </file>
@@ -522,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>8.960000000000001</v>
+        <v>81055</v>
       </c>
       <c r="E2">
-        <v>47.2</v>
+        <v>63.6</v>
       </c>
       <c r="F2">
-        <v>14.87</v>
+        <v>3.68</v>
       </c>
       <c r="G2">
+        <v>60</v>
+      </c>
+      <c r="H2">
         <v>50</v>
       </c>
-      <c r="H2">
-        <v>63</v>
-      </c>
       <c r="I2">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="J2">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="K2">
-        <v>60.2</v>
+        <v>56.9</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -552,10 +549,10 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>66.57973643566133</v>
+        <v>59.14876667115259</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -569,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>14.19</v>
+        <v>197.96</v>
       </c>
       <c r="E3">
-        <v>47.3</v>
+        <v>49</v>
       </c>
       <c r="F3">
-        <v>19.95</v>
+        <v>8.93</v>
       </c>
       <c r="G3">
+        <v>60</v>
+      </c>
+      <c r="H3">
         <v>50</v>
       </c>
-      <c r="H3">
-        <v>40</v>
-      </c>
       <c r="I3">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="J3">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="K3">
-        <v>60.2</v>
+        <v>55.7</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -599,10 +596,10 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>66.57973643566133</v>
+        <v>59.14876667115259</v>
       </c>
       <c r="O3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -616,40 +613,40 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>71406.64999999999</v>
+        <v>13.03</v>
       </c>
       <c r="E4">
-        <v>53.1</v>
+        <v>63.3</v>
       </c>
       <c r="F4">
-        <v>6.75</v>
+        <v>21.55</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H4">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I4">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="J4">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="K4">
-        <v>54</v>
+        <v>53.9</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
       </c>
       <c r="M4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4">
+        <v>59.14876667115259</v>
+      </c>
+      <c r="O4" t="s">
         <v>28</v>
-      </c>
-      <c r="N4">
-        <v>66.57973643566133</v>
-      </c>
-      <c r="O4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -663,40 +660,40 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>123.72</v>
+        <v>23.7</v>
       </c>
       <c r="E5">
-        <v>27.8</v>
+        <v>74.2</v>
       </c>
       <c r="F5">
-        <v>1.88</v>
+        <v>48.31</v>
       </c>
       <c r="G5">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H5">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I5">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J5">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="K5">
-        <v>47.2</v>
+        <v>53.7</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
       </c>
       <c r="M5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5">
+        <v>59.14876667115259</v>
+      </c>
+      <c r="O5" t="s">
         <v>28</v>
-      </c>
-      <c r="N5">
-        <v>66.57973643566133</v>
-      </c>
-      <c r="O5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -710,40 +707,40 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>175.18</v>
+        <v>186.82</v>
       </c>
       <c r="E6">
-        <v>27.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F6">
-        <v>8.949999999999999</v>
+        <v>18.1</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H6">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="I6">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="J6">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="K6">
-        <v>47.2</v>
+        <v>49.9</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
       </c>
       <c r="M6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6">
+        <v>59.14876667115259</v>
+      </c>
+      <c r="O6" t="s">
         <v>28</v>
-      </c>
-      <c r="N6">
-        <v>66.57973643566133</v>
-      </c>
-      <c r="O6" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_비트코인_분석.xlsx
+++ b/DECISION/미장_비트코인_분석.xlsx
@@ -61,7 +61,16 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-05-07</t>
+    <t>2026-06-07</t>
+  </si>
+  <si>
+    <t>Riot Platforms, Inc.</t>
+  </si>
+  <si>
+    <t>MARA Holdings, Inc.</t>
+  </si>
+  <si>
+    <t>Strategy Inc</t>
   </si>
   <si>
     <t>Bitcoin USD</t>
@@ -70,13 +79,13 @@
     <t>Coinbase Global, Inc.</t>
   </si>
   <si>
-    <t>MARA Holdings, Inc.</t>
-  </si>
-  <si>
-    <t>Riot Platforms, Inc.</t>
-  </si>
-  <si>
-    <t>Strategy Inc</t>
+    <t>RIOT</t>
+  </si>
+  <si>
+    <t>MARA</t>
+  </si>
+  <si>
+    <t>MSTR</t>
   </si>
   <si>
     <t>BTC-USD</t>
@@ -85,22 +94,13 @@
     <t>COIN</t>
   </si>
   <si>
-    <t>MARA</t>
-  </si>
-  <si>
-    <t>RIOT</t>
-  </si>
-  <si>
-    <t>MSTR</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>⚪ 중립 구간</t>
+    <t>🔴 강한 긴축 / 리스크</t>
   </si>
 </sst>
 </file>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>81055</v>
+        <v>24.66</v>
       </c>
       <c r="E2">
-        <v>63.6</v>
+        <v>54.9</v>
       </c>
       <c r="F2">
-        <v>3.68</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H2">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I2">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="J2">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="K2">
-        <v>56.9</v>
+        <v>44.9</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>197.96</v>
+        <v>12.32</v>
       </c>
       <c r="E3">
         <v>49</v>
       </c>
       <c r="F3">
-        <v>8.93</v>
+        <v>-14.33</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="J3">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="K3">
-        <v>55.7</v>
+        <v>40.9</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>13.03</v>
+        <v>120.44</v>
       </c>
       <c r="E4">
-        <v>63.3</v>
+        <v>14.4</v>
       </c>
       <c r="F4">
-        <v>21.55</v>
+        <v>-24.29</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H4">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="I4">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="J4">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="K4">
-        <v>53.9</v>
+        <v>24.1</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>23.7</v>
+        <v>60708</v>
       </c>
       <c r="E5">
-        <v>74.2</v>
+        <v>5.5</v>
       </c>
       <c r="F5">
-        <v>48.31</v>
+        <v>-14.88</v>
       </c>
       <c r="G5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>60</v>
       </c>
       <c r="I5">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J5">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="K5">
-        <v>53.7</v>
+        <v>23.9</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>186.82</v>
+        <v>152.4</v>
       </c>
       <c r="E6">
-        <v>70.09999999999999</v>
+        <v>25.5</v>
       </c>
       <c r="F6">
-        <v>18.1</v>
+        <v>-19.38</v>
       </c>
       <c r="G6">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>46</v>
       </c>
       <c r="I6">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J6">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="K6">
-        <v>49.9</v>
+        <v>22.3</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>
